--- a/SUIM/TEST/Report.xlsx
+++ b/SUIM/TEST/Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emanu\Desktop\Mestrado\2A\1S\VCOM\Assignment_2\SUIM\TEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F868D1-DDD1-48DE-B3C0-73D03E898EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D448B9C9-2197-47B1-9431-BF455284CAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -563,7 +563,7 @@
     <t>F1 Score</t>
   </si>
   <si>
-    <t>mIuO</t>
+    <t>mIoU</t>
   </si>
 </sst>
 </file>
@@ -677,8 +677,11 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -686,11 +689,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1615,122 +1615,122 @@
       </c>
     </row>
     <row r="18" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="8" t="s">
         <v>97</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="7" t="str">
-        <f>LEFT(D3, FIND("±", D3) - 1)</f>
+      <c r="D18" s="4" t="str">
+        <f t="shared" ref="D18:I18" si="0">LEFT(D3, FIND("±", D3) - 1)</f>
         <v xml:space="preserve">92.86 </v>
       </c>
-      <c r="E18" s="7" t="str">
-        <f>LEFT(E3, FIND("±", E3) - 1)</f>
+      <c r="E18" s="4" t="str">
+        <f t="shared" si="0"/>
         <v xml:space="preserve">85.98 </v>
       </c>
-      <c r="F18" s="7" t="str">
-        <f>LEFT(F3, FIND("±", F3) - 1)</f>
+      <c r="F18" s="4" t="str">
+        <f t="shared" si="0"/>
         <v xml:space="preserve">80.46 </v>
       </c>
-      <c r="G18" s="7" t="str">
-        <f>LEFT(G3, FIND("±", G3) - 1)</f>
+      <c r="G18" s="4" t="str">
+        <f t="shared" si="0"/>
         <v xml:space="preserve">83.17 </v>
       </c>
-      <c r="H18" s="7" t="str">
-        <f>LEFT(H3, FIND("±", H3) - 1)</f>
+      <c r="H18" s="4" t="str">
+        <f t="shared" si="0"/>
         <v xml:space="preserve">93.23 </v>
       </c>
-      <c r="I18" s="7" t="str">
-        <f>LEFT(I3, FIND("±", I3) - 1)</f>
+      <c r="I18" s="4" t="str">
+        <f t="shared" si="0"/>
         <v xml:space="preserve">87.14 </v>
       </c>
-      <c r="K18" s="5" t="s">
+      <c r="K18" s="6" t="s">
         <v>97</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="M18" s="7" t="str">
-        <f>LEFT(M3, FIND("±", M3) - 1)</f>
+      <c r="M18" s="4" t="str">
+        <f t="shared" ref="M18:R18" si="1">LEFT(M3, FIND("±", M3) - 1)</f>
         <v xml:space="preserve">84.78 </v>
       </c>
-      <c r="N18" s="7" t="str">
-        <f>LEFT(N3, FIND("±", N3) - 1)</f>
+      <c r="N18" s="4" t="str">
+        <f t="shared" si="1"/>
         <v xml:space="preserve">89.29 </v>
       </c>
-      <c r="O18" s="7" t="str">
-        <f>LEFT(O3, FIND("±", O3) - 1)</f>
+      <c r="O18" s="4" t="str">
+        <f t="shared" si="1"/>
         <v xml:space="preserve">75.16 </v>
       </c>
-      <c r="P18" s="7" t="str">
-        <f>LEFT(P3, FIND("±", P3) - 1)</f>
+      <c r="P18" s="4" t="str">
+        <f t="shared" si="1"/>
         <v xml:space="preserve">89.45 </v>
       </c>
-      <c r="Q18" s="7" t="str">
-        <f>LEFT(Q3, FIND("±", Q3) - 1)</f>
+      <c r="Q18" s="4" t="str">
+        <f t="shared" si="1"/>
         <v xml:space="preserve">83.54 </v>
       </c>
-      <c r="R18" s="7" t="str">
-        <f>LEFT(R3, FIND("±", R3) - 1)</f>
+      <c r="R18" s="4" t="str">
+        <f t="shared" si="1"/>
         <v xml:space="preserve">84.44 </v>
       </c>
     </row>
     <row r="19" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="4"/>
+      <c r="B19" s="8"/>
       <c r="C19" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="7" t="str">
-        <f>LEFT(D12, FIND("±", D12) - 1)</f>
+      <c r="D19" s="4" t="str">
+        <f t="shared" ref="D19:I19" si="2">LEFT(D12, FIND("±", D12) - 1)</f>
         <v xml:space="preserve">88.72 </v>
       </c>
-      <c r="E19" s="7" t="str">
-        <f>LEFT(E12, FIND("±", E12) - 1)</f>
+      <c r="E19" s="4" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">57.02 </v>
       </c>
-      <c r="F19" s="7" t="str">
-        <f>LEFT(F12, FIND("±", F12) - 1)</f>
+      <c r="F19" s="4" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">71.93 </v>
       </c>
-      <c r="G19" s="7" t="str">
-        <f>LEFT(G12, FIND("±", G12) - 1)</f>
+      <c r="G19" s="4" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">70.06 </v>
       </c>
-      <c r="H19" s="7" t="str">
-        <f>LEFT(H12, FIND("±", H12) - 1)</f>
+      <c r="H19" s="4" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">83.49 </v>
       </c>
-      <c r="I19" s="7" t="str">
-        <f>LEFT(I12, FIND("±", I12) - 1)</f>
+      <c r="I19" s="4" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">74.24 </v>
       </c>
-      <c r="K19" s="6"/>
+      <c r="K19" s="7"/>
       <c r="L19" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="M19" s="7" t="str">
-        <f>LEFT(M12, FIND("±", M12) - 1)</f>
+      <c r="M19" s="4" t="str">
+        <f t="shared" ref="M19:R19" si="3">LEFT(M12, FIND("±", M12) - 1)</f>
         <v xml:space="preserve">81.06 </v>
       </c>
-      <c r="N19" s="7" t="str">
-        <f>LEFT(N12, FIND("±", N12) - 1)</f>
+      <c r="N19" s="4" t="str">
+        <f t="shared" si="3"/>
         <v xml:space="preserve">77.30 </v>
       </c>
-      <c r="O19" s="7" t="str">
-        <f>LEFT(O12, FIND("±", O12) - 1)</f>
+      <c r="O19" s="4" t="str">
+        <f t="shared" si="3"/>
         <v xml:space="preserve">63.79 </v>
       </c>
-      <c r="P19" s="7" t="str">
-        <f>LEFT(P12, FIND("±", P12) - 1)</f>
+      <c r="P19" s="4" t="str">
+        <f t="shared" si="3"/>
         <v xml:space="preserve">84.39 </v>
       </c>
-      <c r="Q19" s="7" t="str">
-        <f>LEFT(Q12, FIND("±", Q12) - 1)</f>
+      <c r="Q19" s="4" t="str">
+        <f t="shared" si="3"/>
         <v xml:space="preserve">76.43 </v>
       </c>
-      <c r="R19" s="7" t="str">
-        <f>LEFT(R12, FIND("±", R12) - 1)</f>
+      <c r="R19" s="4" t="str">
+        <f t="shared" si="3"/>
         <v xml:space="preserve">76.59 </v>
       </c>
     </row>
@@ -1738,55 +1738,55 @@
       <c r="C20" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="8" t="str">
-        <f>LEFT(D5, FIND("±", D5) - 1)</f>
+      <c r="D20" s="5" t="str">
+        <f t="shared" ref="D20:I21" si="4">LEFT(D5, FIND("±", D5) - 1)</f>
         <v xml:space="preserve">72.33 </v>
       </c>
-      <c r="E20" s="8" t="str">
-        <f>LEFT(E5, FIND("±", E5) - 1)</f>
+      <c r="E20" s="5" t="str">
+        <f t="shared" si="4"/>
         <v xml:space="preserve">42.83 </v>
       </c>
-      <c r="F20" s="8" t="str">
-        <f>LEFT(F5, FIND("±", F5) - 1)</f>
+      <c r="F20" s="5" t="str">
+        <f t="shared" si="4"/>
         <v xml:space="preserve">54.31 </v>
       </c>
-      <c r="G20" s="8" t="str">
-        <f>LEFT(G5, FIND("±", G5) - 1)</f>
+      <c r="G20" s="5" t="str">
+        <f t="shared" si="4"/>
         <v xml:space="preserve">49.20 </v>
       </c>
-      <c r="H20" s="8" t="str">
-        <f>LEFT(H5, FIND("±", H5) - 1)</f>
+      <c r="H20" s="5" t="str">
+        <f t="shared" si="4"/>
         <v xml:space="preserve">69.07 </v>
       </c>
-      <c r="I20" s="8" t="str">
-        <f>LEFT(I5, FIND("±", I5) - 1)</f>
+      <c r="I20" s="5" t="str">
+        <f t="shared" si="4"/>
         <v xml:space="preserve">57.55 </v>
       </c>
       <c r="L20" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="M20" s="8" t="str">
-        <f>LEFT(M5, FIND("±", M5) - 1)</f>
+      <c r="M20" s="5" t="str">
+        <f t="shared" ref="M20:R21" si="5">LEFT(M5, FIND("±", M5) - 1)</f>
         <v xml:space="preserve">66.10 </v>
       </c>
-      <c r="N20" s="8" t="str">
-        <f>LEFT(N5, FIND("±", N5) - 1)</f>
+      <c r="N20" s="5" t="str">
+        <f t="shared" si="5"/>
         <v xml:space="preserve">52.91 </v>
       </c>
-      <c r="O20" s="8" t="str">
-        <f>LEFT(O5, FIND("±", O5) - 1)</f>
+      <c r="O20" s="5" t="str">
+        <f t="shared" si="5"/>
         <v xml:space="preserve">52.48 </v>
       </c>
-      <c r="P20" s="8" t="str">
-        <f>LEFT(P5, FIND("±", P5) - 1)</f>
+      <c r="P20" s="5" t="str">
+        <f t="shared" si="5"/>
         <v xml:space="preserve">68.97 </v>
       </c>
-      <c r="Q20" s="8" t="str">
-        <f>LEFT(Q5, FIND("±", Q5) - 1)</f>
+      <c r="Q20" s="5" t="str">
+        <f t="shared" si="5"/>
         <v xml:space="preserve">61.86 </v>
       </c>
-      <c r="R20" s="8" t="str">
-        <f>LEFT(R5, FIND("±", R5) - 1)</f>
+      <c r="R20" s="5" t="str">
+        <f t="shared" si="5"/>
         <v xml:space="preserve">60.46 </v>
       </c>
     </row>
@@ -1794,55 +1794,55 @@
       <c r="C21" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D21" s="8" t="str">
-        <f>LEFT(D6, FIND("±", D6) - 1)</f>
+      <c r="D21" s="5" t="str">
+        <f t="shared" si="4"/>
         <v xml:space="preserve">64.21 </v>
       </c>
-      <c r="E21" s="8" t="str">
-        <f>LEFT(E6, FIND("±", E6) - 1)</f>
+      <c r="E21" s="5" t="str">
+        <f t="shared" si="4"/>
         <v xml:space="preserve">26.64 </v>
       </c>
-      <c r="F21" s="8" t="str">
-        <f>LEFT(F6, FIND("±", F6) - 1)</f>
+      <c r="F21" s="5" t="str">
+        <f t="shared" si="4"/>
         <v xml:space="preserve">49.10 </v>
       </c>
-      <c r="G21" s="8" t="str">
-        <f>LEFT(G6, FIND("±", G6) - 1)</f>
+      <c r="G21" s="5" t="str">
+        <f t="shared" si="4"/>
         <v xml:space="preserve">31.63 </v>
       </c>
-      <c r="H21" s="8" t="str">
-        <f>LEFT(H6, FIND("±", H6) - 1)</f>
+      <c r="H21" s="5" t="str">
+        <f t="shared" si="4"/>
         <v xml:space="preserve">56.77 </v>
       </c>
-      <c r="I21" s="8" t="str">
-        <f>LEFT(I6, FIND("±", I6) - 1)</f>
+      <c r="I21" s="5" t="str">
+        <f t="shared" si="4"/>
         <v xml:space="preserve">45.67 </v>
       </c>
       <c r="L21" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="M21" s="8" t="str">
-        <f>LEFT(M6, FIND("±", M6) - 1)</f>
+      <c r="M21" s="5" t="str">
+        <f t="shared" si="5"/>
         <v xml:space="preserve">60.31 </v>
       </c>
-      <c r="N21" s="8" t="str">
-        <f>LEFT(N6, FIND("±", N6) - 1)</f>
+      <c r="N21" s="5" t="str">
+        <f t="shared" si="5"/>
         <v xml:space="preserve">40.91 </v>
       </c>
-      <c r="O21" s="8" t="str">
-        <f>LEFT(O6, FIND("±", O6) - 1)</f>
+      <c r="O21" s="5" t="str">
+        <f t="shared" si="5"/>
         <v xml:space="preserve">48.37 </v>
       </c>
-      <c r="P21" s="8" t="str">
-        <f>LEFT(P6, FIND("±", P6) - 1)</f>
+      <c r="P21" s="5" t="str">
+        <f t="shared" si="5"/>
         <v xml:space="preserve">47.83 </v>
       </c>
-      <c r="Q21" s="8" t="str">
-        <f>LEFT(Q6, FIND("±", Q6) - 1)</f>
+      <c r="Q21" s="5" t="str">
+        <f t="shared" si="5"/>
         <v xml:space="preserve">53.62 </v>
       </c>
-      <c r="R21" s="8" t="str">
-        <f>LEFT(R6, FIND("±", R6) - 1)</f>
+      <c r="R21" s="5" t="str">
+        <f t="shared" si="5"/>
         <v xml:space="preserve">50.21 </v>
       </c>
     </row>
@@ -1850,55 +1850,55 @@
       <c r="C22" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D22" s="8" t="str">
-        <f>LEFT(D14, FIND("±", D14) - 1)</f>
+      <c r="D22" s="5" t="str">
+        <f t="shared" ref="D22:I22" si="6">LEFT(D14, FIND("±", D14) - 1)</f>
         <v xml:space="preserve">47.48 </v>
       </c>
-      <c r="E22" s="8" t="str">
-        <f>LEFT(E14, FIND("±", E14) - 1)</f>
+      <c r="E22" s="5" t="str">
+        <f t="shared" si="6"/>
         <v xml:space="preserve">22.20 </v>
       </c>
-      <c r="F22" s="8" t="str">
-        <f>LEFT(F14, FIND("±", F14) - 1)</f>
+      <c r="F22" s="5" t="str">
+        <f t="shared" si="6"/>
         <v xml:space="preserve">31.23 </v>
       </c>
-      <c r="G22" s="8" t="str">
-        <f>LEFT(G14, FIND("±", G14) - 1)</f>
+      <c r="G22" s="5" t="str">
+        <f t="shared" si="6"/>
         <v xml:space="preserve">30.20 </v>
       </c>
-      <c r="H22" s="8" t="str">
-        <f>LEFT(H14, FIND("±", H14) - 1)</f>
+      <c r="H22" s="5" t="str">
+        <f t="shared" si="6"/>
         <v xml:space="preserve">47.23 </v>
       </c>
-      <c r="I22" s="8" t="str">
-        <f>LEFT(I14, FIND("±", I14) - 1)</f>
+      <c r="I22" s="5" t="str">
+        <f t="shared" si="6"/>
         <v xml:space="preserve">35.67 </v>
       </c>
       <c r="L22" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="M22" s="8" t="str">
-        <f>LEFT(M14, FIND("±", M14) - 1)</f>
+      <c r="M22" s="5" t="str">
+        <f t="shared" ref="M22:R22" si="7">LEFT(M14, FIND("±", M14) - 1)</f>
         <v xml:space="preserve">42.73 </v>
       </c>
-      <c r="N22" s="8" t="str">
-        <f>LEFT(N14, FIND("±", N14) - 1)</f>
+      <c r="N22" s="5" t="str">
+        <f t="shared" si="7"/>
         <v xml:space="preserve">24.10 </v>
       </c>
-      <c r="O22" s="8" t="str">
-        <f>LEFT(O14, FIND("±", O14) - 1)</f>
+      <c r="O22" s="5" t="str">
+        <f t="shared" si="7"/>
         <v xml:space="preserve">24.83 </v>
       </c>
-      <c r="P22" s="8" t="str">
-        <f>LEFT(P14, FIND("±", P14) - 1)</f>
+      <c r="P22" s="5" t="str">
+        <f t="shared" si="7"/>
         <v xml:space="preserve">53.34 </v>
       </c>
-      <c r="Q22" s="8" t="str">
-        <f>LEFT(Q14, FIND("±", Q14) - 1)</f>
+      <c r="Q22" s="5" t="str">
+        <f t="shared" si="7"/>
         <v xml:space="preserve">39.69 </v>
       </c>
-      <c r="R22" s="8" t="str">
-        <f>LEFT(R14, FIND("±", R14) - 1)</f>
+      <c r="R22" s="5" t="str">
+        <f t="shared" si="7"/>
         <v xml:space="preserve">36.94 </v>
       </c>
     </row>
@@ -1906,55 +1906,55 @@
       <c r="C23" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D23" s="8" t="str">
-        <f>LEFT(D13, FIND("±", D13) - 1)</f>
+      <c r="D23" s="5" t="str">
+        <f t="shared" ref="D23:I23" si="8">LEFT(D13, FIND("±", D13) - 1)</f>
         <v xml:space="preserve">26.22 </v>
       </c>
-      <c r="E23" s="8" t="str">
-        <f>LEFT(E13, FIND("±", E13) - 1)</f>
+      <c r="E23" s="5" t="str">
+        <f t="shared" si="8"/>
         <v xml:space="preserve">7.75 </v>
       </c>
-      <c r="F23" s="8" t="str">
-        <f>LEFT(F13, FIND("±", F13) - 1)</f>
+      <c r="F23" s="5" t="str">
+        <f t="shared" si="8"/>
         <v xml:space="preserve">6.87 </v>
       </c>
-      <c r="G23" s="8" t="str">
-        <f>LEFT(G13, FIND("±", G13) - 1)</f>
+      <c r="G23" s="5" t="str">
+        <f t="shared" si="8"/>
         <v xml:space="preserve">27.26 </v>
       </c>
-      <c r="H23" s="8" t="str">
-        <f>LEFT(H13, FIND("±", H13) - 1)</f>
+      <c r="H23" s="5" t="str">
+        <f t="shared" si="8"/>
         <v xml:space="preserve">26.33 </v>
       </c>
-      <c r="I23" s="8" t="str">
-        <f>LEFT(I13, FIND("±", I13) - 1)</f>
+      <c r="I23" s="5" t="str">
+        <f t="shared" si="8"/>
         <v xml:space="preserve">18.89 </v>
       </c>
       <c r="L23" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="M23" s="8" t="str">
-        <f>LEFT(M13, FIND("±", M13) - 1)</f>
+      <c r="M23" s="5" t="str">
+        <f t="shared" ref="M23:R23" si="9">LEFT(M13, FIND("±", M13) - 1)</f>
         <v xml:space="preserve">26.59 </v>
       </c>
-      <c r="N23" s="8" t="str">
-        <f>LEFT(N13, FIND("±", N13) - 1)</f>
+      <c r="N23" s="5" t="str">
+        <f t="shared" si="9"/>
         <v xml:space="preserve">12.92 </v>
       </c>
-      <c r="O23" s="8" t="str">
-        <f>LEFT(O13, FIND("±", O13) - 1)</f>
+      <c r="O23" s="5" t="str">
+        <f t="shared" si="9"/>
         <v xml:space="preserve">4.48 </v>
       </c>
-      <c r="P23" s="8" t="str">
-        <f>LEFT(P13, FIND("±", P13) - 1)</f>
+      <c r="P23" s="5" t="str">
+        <f t="shared" si="9"/>
         <v xml:space="preserve">54.22 </v>
       </c>
-      <c r="Q23" s="8" t="str">
-        <f>LEFT(Q13, FIND("±", Q13) - 1)</f>
+      <c r="Q23" s="5" t="str">
+        <f t="shared" si="9"/>
         <v xml:space="preserve">27.52 </v>
       </c>
-      <c r="R23" s="8" t="str">
-        <f>LEFT(R13, FIND("±", R13) - 1)</f>
+      <c r="R23" s="5" t="str">
+        <f t="shared" si="9"/>
         <v xml:space="preserve">25.15 </v>
       </c>
     </row>
@@ -1962,55 +1962,55 @@
       <c r="C24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="7" t="str">
-        <f>LEFT(D11, FIND("±", D11) - 1)</f>
+      <c r="D24" s="4" t="str">
+        <f t="shared" ref="D24:I24" si="10">LEFT(D11, FIND("±", D11) - 1)</f>
         <v xml:space="preserve">73.51 </v>
       </c>
-      <c r="E24" s="7" t="str">
-        <f>LEFT(E11, FIND("±", E11) - 1)</f>
+      <c r="E24" s="4" t="str">
+        <f t="shared" si="10"/>
         <v xml:space="preserve">55.54 </v>
       </c>
-      <c r="F24" s="7" t="str">
-        <f>LEFT(F11, FIND("±", F11) - 1)</f>
+      <c r="F24" s="4" t="str">
+        <f t="shared" si="10"/>
         <v xml:space="preserve">56.75 </v>
       </c>
-      <c r="G24" s="7" t="str">
-        <f>LEFT(G11, FIND("±", G11) - 1)</f>
+      <c r="G24" s="4" t="str">
+        <f t="shared" si="10"/>
         <v xml:space="preserve">47.67 </v>
       </c>
-      <c r="H24" s="7" t="str">
-        <f>LEFT(H11, FIND("±", H11) - 1)</f>
+      <c r="H24" s="4" t="str">
+        <f t="shared" si="10"/>
         <v xml:space="preserve">70.62 </v>
       </c>
-      <c r="I24" s="7" t="str">
-        <f>LEFT(I11, FIND("±", I11) - 1)</f>
+      <c r="I24" s="4" t="str">
+        <f t="shared" si="10"/>
         <v xml:space="preserve">60.82 </v>
       </c>
       <c r="L24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M24" s="7" t="str">
-        <f>LEFT(M11, FIND("±", M11) - 1)</f>
+      <c r="M24" s="4" t="str">
+        <f t="shared" ref="M24:R24" si="11">LEFT(M11, FIND("±", M11) - 1)</f>
         <v xml:space="preserve">70.63 </v>
       </c>
-      <c r="N24" s="7" t="str">
-        <f>LEFT(N11, FIND("±", N11) - 1)</f>
+      <c r="N24" s="4" t="str">
+        <f t="shared" si="11"/>
         <v xml:space="preserve">66.47 </v>
       </c>
-      <c r="O24" s="7" t="str">
-        <f>LEFT(O11, FIND("±", O11) - 1)</f>
+      <c r="O24" s="4" t="str">
+        <f t="shared" si="11"/>
         <v xml:space="preserve">57.68 </v>
       </c>
-      <c r="P24" s="7" t="str">
-        <f>LEFT(P11, FIND("±", P11) - 1)</f>
+      <c r="P24" s="4" t="str">
+        <f t="shared" si="11"/>
         <v xml:space="preserve">70.29 </v>
       </c>
-      <c r="Q24" s="7" t="str">
-        <f>LEFT(Q11, FIND("±", Q11) - 1)</f>
+      <c r="Q24" s="4" t="str">
+        <f t="shared" si="11"/>
         <v xml:space="preserve">67.48 </v>
       </c>
-      <c r="R24" s="7" t="str">
-        <f>LEFT(R11, FIND("±", R11) - 1)</f>
+      <c r="R24" s="4" t="str">
+        <f t="shared" si="11"/>
         <v xml:space="preserve">66.51 </v>
       </c>
       <c r="S24" s="2"/>
@@ -2019,55 +2019,55 @@
       <c r="C25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="8" t="str">
-        <f>LEFT(D10, FIND("±", D10) - 1)</f>
+      <c r="D25" s="5" t="str">
+        <f t="shared" ref="D25:I25" si="12">LEFT(D10, FIND("±", D10) - 1)</f>
         <v xml:space="preserve">53.10 </v>
       </c>
-      <c r="E25" s="8" t="str">
-        <f>LEFT(E10, FIND("±", E10) - 1)</f>
+      <c r="E25" s="5" t="str">
+        <f t="shared" si="12"/>
         <v xml:space="preserve">40.98 </v>
       </c>
-      <c r="F25" s="8" t="str">
-        <f>LEFT(F10, FIND("±", F10) - 1)</f>
+      <c r="F25" s="5" t="str">
+        <f t="shared" si="12"/>
         <v xml:space="preserve">42.64 </v>
       </c>
-      <c r="G25" s="8" t="str">
-        <f>LEFT(G10, FIND("±", G10) - 1)</f>
+      <c r="G25" s="5" t="str">
+        <f t="shared" si="12"/>
         <v xml:space="preserve">40.24 </v>
       </c>
-      <c r="H25" s="8" t="str">
-        <f>LEFT(H10, FIND("±", H10) - 1)</f>
+      <c r="H25" s="5" t="str">
+        <f t="shared" si="12"/>
         <v xml:space="preserve">57.04 </v>
       </c>
-      <c r="I25" s="8" t="str">
-        <f>LEFT(I10, FIND("±", I10) - 1)</f>
+      <c r="I25" s="5" t="str">
+        <f t="shared" si="12"/>
         <v xml:space="preserve">46.80 </v>
       </c>
       <c r="L25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M25" s="8" t="str">
-        <f>LEFT(M10, FIND("±", M10) - 1)</f>
+      <c r="M25" s="5" t="str">
+        <f t="shared" ref="M25:R25" si="13">LEFT(M10, FIND("±", M10) - 1)</f>
         <v xml:space="preserve">56.93 </v>
       </c>
-      <c r="N25" s="8" t="str">
-        <f>LEFT(N10, FIND("±", N10) - 1)</f>
+      <c r="N25" s="5" t="str">
+        <f t="shared" si="13"/>
         <v xml:space="preserve">63.46 </v>
       </c>
-      <c r="O25" s="8" t="str">
-        <f>LEFT(O10, FIND("±", O10) - 1)</f>
+      <c r="O25" s="5" t="str">
+        <f t="shared" si="13"/>
         <v xml:space="preserve">50.03 </v>
       </c>
-      <c r="P25" s="8" t="str">
-        <f>LEFT(P10, FIND("±", P10) - 1)</f>
+      <c r="P25" s="5" t="str">
+        <f t="shared" si="13"/>
         <v xml:space="preserve">65.43 </v>
       </c>
-      <c r="Q25" s="8" t="str">
-        <f>LEFT(Q10, FIND("±", Q10) - 1)</f>
+      <c r="Q25" s="5" t="str">
+        <f t="shared" si="13"/>
         <v xml:space="preserve">59.97 </v>
       </c>
-      <c r="R25" s="8" t="str">
-        <f>LEFT(R10, FIND("±", R10) - 1)</f>
+      <c r="R25" s="5" t="str">
+        <f t="shared" si="13"/>
         <v xml:space="preserve">59.16 </v>
       </c>
     </row>
